--- a/dataset/construct/dataset_splits/data_size/20_percent/lmu/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/lmu/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53993439</v>
+        <v>52778393</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,74 +625,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.6570841889117</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>72.58042436687199</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.2309871275413</v>
+      </c>
       <c r="E2" t="n">
-        <v>25.2493372048984</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>55</v>
+      </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>309</v>
+      </c>
+      <c r="I2" t="n">
+        <v>245</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>165</v>
+      </c>
+      <c r="K2" t="n">
+        <v>719</v>
+      </c>
+      <c r="L2" t="n">
+        <v>301</v>
+      </c>
+      <c r="M2" t="n">
+        <v>81</v>
+      </c>
+      <c r="N2" t="n">
+        <v>126</v>
+      </c>
       <c r="O2" t="n">
-        <v>73</v>
+        <v>508</v>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>28.9</v>
       </c>
       <c r="V2" t="n">
-        <v>49</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>30.08028424436822</v>
       </c>
       <c r="X2" t="n">
-        <v>24.1</v>
+        <v>29.00175931304942</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>431.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -719,30 +718,21 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN2" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51786125</v>
+        <v>54955302</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -750,76 +740,80 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>81.119780971937</v>
+        <v>72.0766598220397</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>26.7036235803137</v>
       </c>
       <c r="E3" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>245</v>
+      </c>
+      <c r="M3" t="n">
+        <v>59</v>
+      </c>
+      <c r="N3" t="n">
+        <v>41</v>
+      </c>
       <c r="O3" t="n">
-        <v>352.80658</v>
+        <v>345</v>
       </c>
       <c r="P3" t="n">
-        <v>394.73203</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>392.3589</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1139.8975</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>23.90507245240268</v>
       </c>
       <c r="X3" t="n">
-        <v>23.916914</v>
+        <v>22.64643213884526</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>75.77126</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>435.73163</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -828,29 +822,24 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>168</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52968346</v>
+        <v>52310176</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -858,73 +847,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.9363449691992</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>75.28815879534569</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23.8894628099174</v>
+      </c>
       <c r="E4" t="n">
-        <v>26.5432098765432</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>46</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>897</v>
+      </c>
+      <c r="I4" t="n">
+        <v>324</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>1580</v>
       </c>
       <c r="L4" t="n">
-        <v>997</v>
+        <v>516</v>
       </c>
       <c r="M4" t="n">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>1761</v>
+        <v>199</v>
       </c>
       <c r="O4" t="n">
-        <v>179</v>
+        <v>762</v>
       </c>
       <c r="P4" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1212</v>
+        <v>123</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>27.05634032562221</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>26.55889131314182</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>555.3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -933,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -951,24 +946,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>236</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54623649</v>
+        <v>52485232</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -976,65 +962,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.49897330595481</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>83.9616700889802</v>
+      </c>
+      <c r="D5" t="n">
+        <v>29.296875</v>
+      </c>
       <c r="E5" t="n">
-        <v>29.0174471992654</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>36</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>305</v>
+      </c>
+      <c r="I5" t="n">
+        <v>371</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>304</v>
+      </c>
+      <c r="K5" t="n">
+        <v>980</v>
+      </c>
+      <c r="L5" t="n">
+        <v>266</v>
+      </c>
+      <c r="M5" t="n">
+        <v>93</v>
+      </c>
+      <c r="N5" t="n">
+        <v>191</v>
+      </c>
       <c r="O5" t="n">
-        <v>763</v>
+        <v>550</v>
       </c>
       <c r="P5" t="n">
-        <v>412</v>
+        <v>107</v>
       </c>
       <c r="Q5" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1639</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>69</v>
+        <v>24.2</v>
       </c>
       <c r="V5" t="n">
-        <v>165</v>
+        <v>0.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>24.54169222477026</v>
       </c>
       <c r="X5" t="n">
-        <v>22.9</v>
+        <v>23.58825303088947</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>73.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>390.4</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1052,33 +1052,20 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>184</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>156</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54397745</v>
+        <v>55572971</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1086,109 +1073,102 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>91.668720054757</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>72.8459958932238</v>
+      </c>
+      <c r="D6" t="n">
+        <v>23.1481481481481</v>
+      </c>
       <c r="E6" t="n">
-        <v>25.2173585757838</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>63</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>278.38293</v>
+      </c>
+      <c r="M6" t="n">
+        <v>227.9646</v>
+      </c>
+      <c r="N6" t="n">
+        <v>201.513</v>
+      </c>
       <c r="O6" t="n">
-        <v>252</v>
+        <v>707.86053</v>
       </c>
       <c r="P6" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="Q6" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>420</v>
+        <v>58</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>202</v>
+        <v>28.915712</v>
       </c>
       <c r="V6" t="n">
-        <v>672</v>
+        <v>0.26</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>30.3684501843304</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>28.91211526347374</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>71.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>347.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>189</v>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52757719</v>
+        <v>53994432</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1196,113 +1176,102 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77.91649555099249</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>79.62765229295</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30.4705215419501</v>
+      </c>
       <c r="E7" t="n">
-        <v>20.8304498269896</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51</v>
+      </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>237</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>145</v>
+        <v>399</v>
       </c>
       <c r="M7" t="n">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="N7" t="n">
-        <v>610</v>
+        <v>354</v>
       </c>
       <c r="O7" t="n">
-        <v>237</v>
+        <v>1001</v>
       </c>
       <c r="P7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>14</v>
+        <v>24.7</v>
       </c>
       <c r="V7" t="n">
-        <v>73</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>25.56028386055839</v>
       </c>
       <c r="X7" t="n">
-        <v>25.3</v>
+        <v>24.92671052968601</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>81.3</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>490.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54665625</v>
+        <v>54858035</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1310,74 +1279,80 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84.413415468857</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>80.02190280629711</v>
+      </c>
+      <c r="D8" t="n">
+        <v>28.0864197530864</v>
+      </c>
       <c r="E8" t="n">
-        <v>23.2254318478734</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>55</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>539</v>
+      </c>
+      <c r="M8" t="n">
+        <v>405</v>
+      </c>
+      <c r="N8" t="n">
+        <v>335</v>
+      </c>
       <c r="O8" t="n">
-        <v>294</v>
+        <v>1279</v>
       </c>
       <c r="P8" t="n">
-        <v>277</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>89</v>
+        <v>25.2</v>
       </c>
       <c r="V8" t="n">
-        <v>114</v>
+        <v>0.24</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>26.6107064849649</v>
       </c>
       <c r="X8" t="n">
-        <v>22.8</v>
+        <v>25.69882004789576</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>76.5</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>417.5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1386,33 +1361,20 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>184</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>134</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>53327738</v>
+        <v>53057188</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1420,113 +1382,114 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.6105407255305</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>79.9452429842574</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21.359306249733</v>
+      </c>
       <c r="E9" t="n">
-        <v>27.2493063812921</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>55</v>
+      </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="I9" t="n">
+        <v>114</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="K9" t="n">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>376</v>
+        <v>68</v>
       </c>
       <c r="O9" t="n">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="P9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>25.2419739743746</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>24.65192152149794</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>77.3</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>449.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52110246</v>
+        <v>52968346</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1534,68 +1497,82 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>73.71937029431901</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>88.9363449691992</v>
+      </c>
+      <c r="D10" t="n">
+        <v>26.5432098765432</v>
+      </c>
       <c r="E10" t="n">
-        <v>21.0667432730058</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>46</v>
+      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>75</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>382</v>
+      </c>
+      <c r="I10" t="n">
+        <v>997</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>381</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1760</v>
+      </c>
+      <c r="L10" t="n">
+        <v>179</v>
+      </c>
+      <c r="M10" t="n">
+        <v>777</v>
+      </c>
+      <c r="N10" t="n">
+        <v>255</v>
+      </c>
       <c r="O10" t="n">
-        <v>335.40356</v>
+        <v>1211</v>
       </c>
       <c r="P10" t="n">
-        <v>299.01544</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>159.00027</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>793.4194</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>27.53380515489789</v>
       </c>
       <c r="X10" t="n">
-        <v>25.28954</v>
+        <v>26.59003420816596</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>80.04646</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>475.6914</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1604,39 +1581,30 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>153</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>106</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52530187</v>
+        <v>54414814</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1644,121 +1612,106 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>78.5516769336071</v>
+        <v>80.90349075975359</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25.5036157024793</v>
       </c>
       <c r="E11" t="n">
-        <v>27.9296875</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>96</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="M11" t="n">
-        <v>258</v>
+        <v>172</v>
       </c>
       <c r="N11" t="n">
-        <v>433</v>
+        <v>100</v>
       </c>
       <c r="O11" t="n">
-        <v>72</v>
+        <v>388</v>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>19</v>
+        <v>27.2</v>
       </c>
       <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>27.18366428009573</v>
+      </c>
+      <c r="X11" t="n">
+        <v>26.89237924411993</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>165</v>
+      </c>
+      <c r="AK11" t="n">
         <v>155</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>442.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53136667</v>
+        <v>51767598</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1766,85 +1719,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.5537303216975</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>79.08555783709789</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25.992438563327</v>
+      </c>
       <c r="E12" t="n">
-        <v>27.1707711874205</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I12" t="n">
+        <v>291</v>
+      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="K12" t="n">
-        <v>61</v>
+        <v>509</v>
       </c>
       <c r="L12" t="n">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="M12" t="n">
-        <v>143</v>
+        <v>291</v>
       </c>
       <c r="N12" t="n">
-        <v>520</v>
+        <v>138</v>
       </c>
       <c r="O12" t="n">
-        <v>61</v>
+        <v>509</v>
       </c>
       <c r="P12" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>29.79380534680281</v>
       </c>
       <c r="X12" t="n">
-        <v>30.3</v>
+        <v>28.91602339581951</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>97.7</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>685.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1859,24 +1818,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>51407442</v>
+        <v>52386464</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1884,89 +1834,91 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>89.1006160164271</v>
+        <v>82.11909650924029</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>24.3827160493827</v>
       </c>
       <c r="E13" t="n">
-        <v>23.8894628099174</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="I13" t="n">
+        <v>546</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="K13" t="n">
-        <v>622</v>
+        <v>1171</v>
       </c>
       <c r="L13" t="n">
-        <v>547</v>
+        <v>243</v>
       </c>
       <c r="M13" t="n">
-        <v>339</v>
+        <v>540</v>
       </c>
       <c r="N13" t="n">
-        <v>1508</v>
+        <v>368</v>
       </c>
       <c r="O13" t="n">
-        <v>594</v>
+        <v>1151</v>
       </c>
       <c r="P13" t="n">
-        <v>509</v>
+        <v>17</v>
       </c>
       <c r="Q13" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1345</v>
+        <v>18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>31.73549565252393</v>
       </c>
       <c r="X13" t="n">
-        <v>30.5</v>
+        <v>31.00887782851864</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>99.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>725.4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -1981,24 +1933,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
         <v>186</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>53719519</v>
+        <v>51804346</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2006,67 +1949,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90.3846680355921</v>
+        <v>77.264887063655</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>18.3654729109275</v>
       </c>
       <c r="E14" t="n">
-        <v>22.4996371026274</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55</v>
+      </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>358</v>
+      </c>
+      <c r="I14" t="n">
+        <v>780</v>
+      </c>
       <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>430</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1568</v>
+      </c>
+      <c r="L14" t="n">
+        <v>306</v>
+      </c>
+      <c r="M14" t="n">
+        <v>369</v>
+      </c>
+      <c r="N14" t="n">
+        <v>430</v>
+      </c>
       <c r="O14" t="n">
-        <v>715.8074</v>
+        <v>1105</v>
       </c>
       <c r="P14" t="n">
-        <v>587.9471</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="n">
-        <v>313.37814</v>
+        <v>65</v>
       </c>
       <c r="R14" t="n">
-        <v>1617.1327</v>
+        <v>513</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>26.29239659878111</v>
       </c>
       <c r="X14" t="n">
-        <v>25.97578</v>
+        <v>24.81664698923684</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>81.47221999999999</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>506.72342</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2084,33 +2039,24 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>196</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55300994</v>
+        <v>54269607</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2118,74 +2064,80 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82.85284052019161</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>80.6598220396988</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.1632653061225</v>
+      </c>
       <c r="E15" t="n">
-        <v>32.2420634920635</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
-        <v>65</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>203</v>
+      </c>
+      <c r="M15" t="n">
+        <v>298</v>
+      </c>
+      <c r="N15" t="n">
+        <v>209</v>
+      </c>
       <c r="O15" t="n">
-        <v>490</v>
+        <v>710</v>
       </c>
       <c r="P15" t="n">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="Q15" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1254</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="T15" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V15" t="n">
-        <v>46</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>24.06422739549457</v>
       </c>
       <c r="X15" t="n">
-        <v>28</v>
+        <v>23.7924841407797</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>99.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2203,24 +2155,15 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>106</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>52532268</v>
+        <v>52002127</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2228,83 +2171,77 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78.1382614647502</v>
+        <v>79.1457905544148</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>23.3376844270401</v>
       </c>
       <c r="E16" t="n">
-        <v>29.4117647058824</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>74</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>470.25052</v>
       </c>
       <c r="M16" t="n">
-        <v>115</v>
+        <v>270.54822</v>
       </c>
       <c r="N16" t="n">
-        <v>199</v>
+        <v>267.60825</v>
       </c>
       <c r="O16" t="n">
-        <v>74</v>
+        <v>1008.40699</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>133</v>
+        <v>24.251816</v>
       </c>
       <c r="V16" t="n">
-        <v>166</v>
+        <v>0.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>25.00492064438638</v>
       </c>
       <c r="X16" t="n">
-        <v>28</v>
+        <v>24.06106587102134</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>93.5</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>611.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2316,33 +2253,24 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>206</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>186</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53783942</v>
+        <v>52551135</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2350,84 +2278,88 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>89.43737166324431</v>
+        <v>85.990417522245</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>27.0640515887601</v>
       </c>
       <c r="E17" t="n">
-        <v>25.8805706350208</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55</v>
+      </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="I17" t="n">
+        <v>135</v>
+      </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
-        <v>539</v>
+        <v>319</v>
       </c>
       <c r="L17" t="n">
-        <v>860</v>
+        <v>134</v>
       </c>
       <c r="M17" t="n">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="N17" t="n">
-        <v>1723</v>
+        <v>50</v>
       </c>
       <c r="O17" t="n">
-        <v>495</v>
+        <v>319</v>
       </c>
       <c r="P17" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1459</v>
+        <v>15</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>30.36676314193363</v>
       </c>
       <c r="X17" t="n">
-        <v>30.9</v>
+        <v>28.48570802805714</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>100.4</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>755.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2445,24 +2377,15 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>186</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55572971</v>
+        <v>53237839</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2470,74 +2393,88 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>72.8459958932238</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>71.5482546201232</v>
+      </c>
+      <c r="D18" t="n">
+        <v>23.7654320987654</v>
+      </c>
       <c r="E18" t="n">
-        <v>23.1481481481481</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>434</v>
+      </c>
+      <c r="I18" t="n">
+        <v>559</v>
+      </c>
       <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>424</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1417</v>
+      </c>
+      <c r="L18" t="n">
+        <v>374</v>
+      </c>
+      <c r="M18" t="n">
+        <v>346</v>
+      </c>
+      <c r="N18" t="n">
+        <v>322</v>
+      </c>
       <c r="O18" t="n">
-        <v>278.38293</v>
+        <v>1042</v>
       </c>
       <c r="P18" t="n">
-        <v>227.9646</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>201.513</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>707.8606</v>
+        <v>125</v>
       </c>
       <c r="S18" t="n">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="V18" t="n">
-        <v>58</v>
+        <v>0.24</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>27.05634032562221</v>
       </c>
       <c r="X18" t="n">
-        <v>28.915712</v>
+        <v>26.34952606298801</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>95.4053</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>656.5225</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2555,20 +2492,15 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+        <v>132</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>52386464</v>
+        <v>55095784</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2576,83 +2508,77 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>82.11909650924029</v>
+        <v>87.69609856262829</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>24.6755002704164</v>
       </c>
       <c r="E19" t="n">
-        <v>24.3827160493827</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>28</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>257</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>546</v>
+        <v>114</v>
       </c>
       <c r="M19" t="n">
-        <v>368</v>
+        <v>54</v>
       </c>
       <c r="N19" t="n">
-        <v>1171</v>
+        <v>113</v>
       </c>
       <c r="O19" t="n">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="P19" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1152</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>22.8</v>
       </c>
       <c r="V19" t="n">
-        <v>35</v>
+        <v>0.26</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>24.06422739549457</v>
       </c>
       <c r="X19" t="n">
-        <v>30.6</v>
+        <v>23.13590077361723</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>99.7</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>755.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2661,36 +2587,23 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>262</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>186</v>
-      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52251028</v>
+        <v>53849175</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2698,79 +2611,77 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79.9288158795346</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>89.0485968514716</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19.3337299226651</v>
+      </c>
       <c r="E20" t="n">
-        <v>25.8645124716553</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>55</v>
+      </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="n">
-        <v>55</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>269</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>745</v>
+        <v>207</v>
       </c>
       <c r="M20" t="n">
-        <v>511</v>
+        <v>141</v>
       </c>
       <c r="N20" t="n">
-        <v>1525</v>
+        <v>121</v>
       </c>
       <c r="O20" t="n">
-        <v>267</v>
+        <v>469</v>
       </c>
       <c r="P20" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1065</v>
+        <v>119</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>23.8732414637843</v>
       </c>
       <c r="X20" t="n">
-        <v>26.1</v>
+        <v>23.30587886744502</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>90.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>602.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -2791,24 +2702,15 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>174</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52374744</v>
+        <v>54196393</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2816,73 +2718,71 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>81.15263518138261</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>91.93429158110879</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22.5981404958678</v>
+      </c>
       <c r="E21" t="n">
-        <v>25.3086419753086</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38</v>
+      </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="n">
-        <v>45</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1080</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>646</v>
+        <v>171</v>
       </c>
       <c r="M21" t="n">
-        <v>766</v>
+        <v>218</v>
       </c>
       <c r="N21" t="n">
-        <v>2492</v>
+        <v>226</v>
       </c>
       <c r="O21" t="n">
-        <v>901</v>
+        <v>615</v>
       </c>
       <c r="P21" t="n">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>749</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2263</v>
+        <v>26</v>
       </c>
       <c r="S21" t="n">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="T21" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>25.2</v>
       </c>
       <c r="V21" t="n">
-        <v>218</v>
+        <v>0.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>25.68760781503191</v>
       </c>
       <c r="X21" t="n">
-        <v>30.8</v>
+        <v>24.93692430209976</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>99.3</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>749.8</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2900,29 +2800,24 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+        <v>206</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51184093</v>
+        <v>53421842</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2930,117 +2825,114 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79.8302532511978</v>
+        <v>72.67077344284741</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>32.297866163449</v>
       </c>
       <c r="E22" t="n">
-        <v>15.1925078043704</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>76</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>843</v>
+      </c>
+      <c r="I22" t="n">
+        <v>468</v>
+      </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="K22" t="n">
-        <v>460</v>
+        <v>1969</v>
       </c>
       <c r="L22" t="n">
-        <v>242</v>
+        <v>834</v>
       </c>
       <c r="M22" t="n">
-        <v>138</v>
+        <v>468</v>
       </c>
       <c r="N22" t="n">
-        <v>839</v>
+        <v>658</v>
       </c>
       <c r="O22" t="n">
-        <v>455</v>
+        <v>1960</v>
       </c>
       <c r="P22" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="V22" t="n">
-        <v>37</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>29.85746732403956</v>
       </c>
       <c r="X22" t="n">
-        <v>23.3</v>
+        <v>27.85291465191991</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>71.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>384.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
+        <v>149</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>53826725</v>
+        <v>52800188</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3048,109 +2940,110 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>87.791923340178</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>93.68104038329911</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23.4256055363322</v>
+      </c>
       <c r="E23" t="n">
-        <v>27.1415823914337</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>55</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="I23" t="n">
+        <v>130</v>
+      </c>
       <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="K23" t="n">
+        <v>525</v>
+      </c>
+      <c r="L23" t="n">
+        <v>247</v>
+      </c>
+      <c r="M23" t="n">
+        <v>130</v>
+      </c>
+      <c r="N23" t="n">
+        <v>102</v>
+      </c>
       <c r="O23" t="n">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="Q23" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>27.02450933700383</v>
       </c>
       <c r="X23" t="n">
-        <v>21.7</v>
+        <v>26.76424046872996</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>68.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>132</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>163</v>
-      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>53512926</v>
+        <v>53352700</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3158,119 +3051,114 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>82.9979466119097</v>
+        <v>78.24503764544831</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>29.0659268067116</v>
       </c>
       <c r="E24" t="n">
-        <v>23.1246703720232</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40</v>
+      </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="I24" t="n">
+        <v>318</v>
+      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K24" t="n">
-        <v>722</v>
+        <v>691</v>
       </c>
       <c r="L24" t="n">
-        <v>793</v>
+        <v>189</v>
       </c>
       <c r="M24" t="n">
-        <v>555</v>
+        <v>296</v>
       </c>
       <c r="N24" t="n">
-        <v>2070</v>
+        <v>184</v>
       </c>
       <c r="O24" t="n">
-        <v>404</v>
+        <v>669</v>
       </c>
       <c r="P24" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>29.47549546061902</v>
       </c>
       <c r="X24" t="n">
-        <v>28</v>
+        <v>28.60168539601018</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>578.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>183</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54816866</v>
+        <v>55509378</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3278,65 +3166,71 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>85.9301848049281</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>72.13689253935659</v>
+      </c>
+      <c r="D25" t="n">
+        <v>31.8877551020408</v>
+      </c>
       <c r="E25" t="n">
-        <v>32.5963718820862</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>55</v>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>338.7251</v>
+      </c>
+      <c r="M25" t="n">
+        <v>281.04163</v>
+      </c>
+      <c r="N25" t="n">
+        <v>210.4855</v>
+      </c>
       <c r="O25" t="n">
-        <v>192</v>
+        <v>830.2522300000001</v>
       </c>
       <c r="P25" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="Q25" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>21.628544</v>
       </c>
       <c r="V25" t="n">
-        <v>16</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>24.90824834040293</v>
       </c>
       <c r="X25" t="n">
-        <v>23.7</v>
+        <v>22.98045221482684</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>82.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>441.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3354,33 +3248,24 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>252</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54506366</v>
+        <v>54406640</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3388,74 +3273,80 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>79.90143737166321</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>88.8980150581793</v>
+      </c>
+      <c r="D26" t="n">
+        <v>29.2421086364365</v>
+      </c>
       <c r="E26" t="n">
-        <v>23.6340330075308</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>60</v>
+      </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>320</v>
+      </c>
+      <c r="M26" t="n">
+        <v>191</v>
+      </c>
+      <c r="N26" t="n">
+        <v>119</v>
+      </c>
       <c r="O26" t="n">
-        <v>63</v>
+        <v>630</v>
       </c>
       <c r="P26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>20.34000172714422</v>
       </c>
       <c r="X26" t="n">
-        <v>20.8</v>
+        <v>19.29825294774206</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>67.7</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>331.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3464,29 +3355,24 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
+        <v>174</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>54908834</v>
+        <v>52019383</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3494,65 +3380,79 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>82.2231348391513</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>80.9199178644764</v>
+      </c>
+      <c r="D27" t="n">
+        <v>21.9773511187082</v>
+      </c>
       <c r="E27" t="n">
-        <v>29.7619047619048</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>46</v>
+      </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>55</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>443</v>
+      </c>
+      <c r="I27" t="n">
+        <v>485</v>
+      </c>
       <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>384</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="L27" t="n">
+        <v>443</v>
+      </c>
+      <c r="M27" t="n">
+        <v>485</v>
+      </c>
+      <c r="N27" t="n">
+        <v>384</v>
+      </c>
       <c r="O27" t="n">
-        <v>482</v>
+        <v>1312</v>
       </c>
       <c r="P27" t="n">
-        <v>500</v>
+        <v>64</v>
       </c>
       <c r="Q27" t="n">
-        <v>726</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1709</v>
+        <v>16</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>130</v>
+        <v>28.8</v>
       </c>
       <c r="V27" t="n">
-        <v>137</v>
+        <v>0.14</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>29.09352359719847</v>
       </c>
       <c r="X27" t="n">
-        <v>30.1</v>
+        <v>28.58610046527906</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>99.3</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>660.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3561,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3579,19 +3479,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
